--- a/data/usa/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/usa/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG7"/>
+  <dimension ref="A1:BG20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,94 +525,94 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -625,97 +625,97 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -727,16 +727,16 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>trWntSE7</t>
+          <t>foKU4Bi8</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45542.97916666666</v>
+        <v>45549.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">montero r 
-  cos </t>
+          <t xml:space="preserve">demianchuk s 
+  usa </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -784,119 +784,119 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>lAVQ9RGh</t>
+          <t>UFWZoX9L</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-3.5</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>-0.6666666666666665</v>
       </c>
       <c r="V2" t="n">
-        <v>-3.5</v>
+        <v>6.5</v>
       </c>
       <c r="W2" t="n">
-        <v>-2.333333333333334</v>
+        <v>-6.5</v>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1666666666666643</v>
+        <v>-1</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.1666666666666643</v>
+        <v>2.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>-4</v>
+        <v>-2.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>-4.333333333333332</v>
+        <v>-5.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.5</v>
+        <v>-1.5</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>0.5</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.5</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="AL2" t="n">
-        <v>66.25909090909092</v>
+        <v>65.99081289081289</v>
       </c>
       <c r="AM2" t="n">
-        <v>67.0962962962963</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-0.1166108991963739</v>
-      </c>
+        <v>65.47979797979798</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
+      <c r="AP2" t="n">
+        <v>0.36944444444444</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-2.859090909090867</v>
+      </c>
       <c r="AR2" t="n">
-        <v>0.8936259779551534</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-0.03521181199752621</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
+        <v>-161485.4139218265</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>0.1474747474747318</v>
+      </c>
       <c r="AU2" t="n">
-        <v>-0.2036363636363667</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.565223665223684</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
+        <v>-1.091482213438734</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-0.7027964426877418</v>
+      </c>
       <c r="AX2" t="n">
-        <v>-0.05584415584415603</v>
+        <v>0.121998243302599</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.3254869264119407</v>
+        <v>-161568.1818181812</v>
       </c>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
-        <v>-2.002732126135299</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-828393.0151684138</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-5.526378066378101</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.474834054834048</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="n">
-        <v>1072554.112554112</v>
-      </c>
+        <v>-1.608271848924062</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="n">
+        <v>-0.8689393939393959</v>
+      </c>
+      <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="n">
         <v>0</v>
       </c>
@@ -904,32 +904,32 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SvbdWyTh</t>
+          <t>l8RwqFCb</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45542.89583333334</v>
+        <v>45549.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">de oliveira m 
+          <t xml:space="preserve">villarreal a 
   usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">soldier field
-  chicago  il </t>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -956,22 +956,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>6LuGZiZI</t>
+          <t>WSL0wFD4</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>nJ01AhXP</t>
+          <t>86yPt28f</t>
         </is>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Q3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -980,100 +980,100 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>4</v>
+        <v>11.83333333333334</v>
       </c>
       <c r="W3" t="n">
-        <v>4.5</v>
+        <v>-11.83333333333334</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>-2.5</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="AA3" t="n">
-        <v>2</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AB3" t="n">
-        <v>16.5</v>
+        <v>5.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>-16.5</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>-6.333333333333334</v>
       </c>
       <c r="AE3" t="n">
-        <v>-6</v>
+        <v>-3.666666666666666</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.5</v>
+        <v>5.833333333333334</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.5</v>
+        <v>-5</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>-2.5</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.5</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AL3" t="n">
-        <v>68.81666666666666</v>
+        <v>67.02592592592593</v>
       </c>
       <c r="AM3" t="n">
-        <v>65.02525252525251</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.166895726635435</v>
-      </c>
+        <v>69.303367003367</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
+      <c r="AP3" t="n">
+        <v>-0.5393939393939178</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-2.901515151515071</v>
+      </c>
       <c r="AR3" t="n">
-        <v>3.250717373143011</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>-0.003581871345029297</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
+        <v>-195358.7662803028</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="n">
+        <v>-1.724242424242419</v>
+      </c>
       <c r="AU3" t="n">
-        <v>-0.8088888888888839</v>
+        <v>-0.3212121212121213</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.238383838383825</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
+        <v>-0.5869834363835906</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-2.645087391681813</v>
+      </c>
       <c r="AX3" t="n">
-        <v>-0.009494949494949667</v>
+        <v>-3.575608910496683</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.3875354146234997</v>
+        <v>-126818.1818181821</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>-2.523432902909462</v>
+        <v>0.04910192147034254</v>
       </c>
       <c r="BB3" t="n">
-        <v>211737.3926210454</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>-0.4975757575757598</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1.394141414141416</v>
-      </c>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="n">
-        <v>1010212.121212122</v>
-      </c>
+        <v>0.4651770543411544</v>
+      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="n">
+        <v>-2.169696969696972</v>
+      </c>
+      <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="n">
         <v>0</v>
       </c>
@@ -1081,32 +1081,32 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AoWGqXpJ</t>
+          <t>AHSZqech</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45542.89583333334</v>
+        <v>45549.9375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">villarreal a 
+          <t xml:space="preserve">szpala l 
   usa </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">shell energy stadium
-  houston  tx </t>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>txUJt9AR</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1133,124 +1133,124 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>UL7r7duf</t>
+          <t>WWvwigh8</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>86yPt28f</t>
+          <t>tOpyQa24</t>
         </is>
       </c>
       <c r="O4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
         <v>-1</v>
       </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
       <c r="V4" t="n">
-        <v>13</v>
+        <v>-12</v>
       </c>
       <c r="W4" t="n">
-        <v>-9</v>
+        <v>12</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>-2.5</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="n">
         <v>2</v>
       </c>
-      <c r="AB4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-30</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AE4" t="n">
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK4" t="n">
         <v>-3</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1</v>
-      </c>
       <c r="AL4" t="n">
-        <v>66</v>
+        <v>65.72727272727273</v>
       </c>
       <c r="AM4" t="n">
-        <v>69.67777777777778</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0.8933953542904973</v>
-      </c>
+        <v>70.90000000000001</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
+      <c r="AP4" t="n">
+        <v>-1.974949494949499</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>2.230101010101009</v>
+      </c>
       <c r="AR4" t="n">
-        <v>-1.898187859313182</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-0.008333333333333304</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
+        <v>-870581.7193675886</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="n">
+        <v>-4.219191919191914</v>
+      </c>
       <c r="AU4" t="n">
-        <v>-1.236127946127951</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>-3.096767676767683</v>
-      </c>
-      <c r="AW4" t="inlineStr"/>
+        <v>-4.098359683794463</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-8.343504611330687</v>
+      </c>
       <c r="AX4" t="n">
-        <v>-0.2086195286195285</v>
+        <v>-1.317490118577084</v>
       </c>
       <c r="AY4" t="n">
-        <v>-5.314299894478935</v>
+        <v>-784008.0808080807</v>
       </c>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>-1.39249839532448</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>-832351.6807858241</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.3602020202019958</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>-3.624074074074073</v>
-      </c>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="n">
-        <v>-1980099.831649831</v>
-      </c>
+        <v>-1.043474967061911</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="n">
+        <v>-2.376161616161614</v>
+      </c>
+      <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
@@ -1258,32 +1258,32 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hIoLKAg0</t>
+          <t>xUcLQXdU</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45542.85416666666</v>
+        <v>45549.89583333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">szpala l 
+          <t xml:space="preserve">marrufo j 
   usa </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">lower com field
-  columbus  oh </t>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1310,120 +1310,120 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>zoZ995af</t>
+          <t>6LuGZiZI</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>tOpyQa24</t>
+          <t>6BusaLE3</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-3</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-1</v>
+      </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>8.25</v>
+        <v>4</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.25</v>
+        <v>-4</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.25</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>17.75</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>-17.75</v>
+        <v>4</v>
       </c>
       <c r="AD5" t="n">
-        <v>-6.75</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
-        <v>-5.75</v>
+        <v>5</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1</v>
       </c>
-      <c r="AK5" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AL5" t="n">
-        <v>67.30113636363637</v>
+        <v>69.26010101010101</v>
       </c>
       <c r="AM5" t="n">
-        <v>68.45420875420875</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-0.6755634595228592</v>
-      </c>
+        <v>69.45454545454545</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
+      <c r="AP5" t="n">
+        <v>-1.738181818181829</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>2.548484848484833</v>
+      </c>
       <c r="AR5" t="n">
-        <v>-1.691668503509121</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-0.1835398017902814</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
+        <v>-169856.8220823801</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="n">
+        <v>2.850303030303039</v>
+      </c>
       <c r="AU5" t="n">
-        <v>-1.005082070707065</v>
+        <v>0.09090909090909105</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.3754734848484844</v>
-      </c>
-      <c r="AW5" t="inlineStr"/>
+        <v>1.519433320620397</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.8477599796593012</v>
+      </c>
       <c r="AX5" t="n">
-        <v>-0.1770833333333333</v>
+        <v>-2.031821128909215</v>
       </c>
       <c r="AY5" t="n">
-        <v>-2.005499802218949</v>
+        <v>326151.5151515156</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>2.366903976422833</v>
+        <v>0.00694444444444442</v>
       </c>
       <c r="BB5" t="n">
-        <v>-722775.4823301695</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.867708333333354</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>-1.19709595959597</v>
-      </c>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="n">
-        <v>941120.8964646463</v>
-      </c>
+        <v>-0.487123379099927</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="n">
+        <v>3.997575757575763</v>
+      </c>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
@@ -1431,32 +1431,32 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EyfhXHDn</t>
+          <t>EkZQoHSu</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45542.85416666666</v>
+        <v>45549.89583333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">mendoza r 
+          <t xml:space="preserve">bazakos f 
   usa </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  harrison  nj </t>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1483,122 +1483,124 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>rJ9D8rzj</t>
+          <t>UL7r7duf</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>txm4BKVR</t>
+          <t>GzULyFoh</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
-      </c>
-      <c r="R6" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.666666666666666</v>
+        <v>15</v>
       </c>
       <c r="W6" t="n">
-        <v>-5.333333333333333</v>
+        <v>-15</v>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-1.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-1</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3333333333333357</v>
+        <v>0.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.3333333333333357</v>
+        <v>-1.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.3333333333333339</v>
+        <v>-3.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.5</v>
+        <v>5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>67.73939393939393</v>
+        <v>70.32878787878788</v>
       </c>
       <c r="AM6" t="n">
-        <v>69</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>-2.878653658433073</v>
-      </c>
+        <v>69.33333333333334</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
+      <c r="AP6" t="n">
+        <v>-0.3907070707070659</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.920606060606076</v>
+      </c>
       <c r="AR6" t="n">
-        <v>-0.8844004707146027</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-0.08701217329036903</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
+        <v>-353229.0914470581</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>2.217979797979808</v>
+      </c>
       <c r="AU6" t="n">
-        <v>-5.295670995670996</v>
+        <v>0.1927272727272729</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.808225108225102</v>
-      </c>
-      <c r="AW6" t="inlineStr"/>
+        <v>-0.8755639870217884</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-0.8768246473617154</v>
+      </c>
       <c r="AX6" t="n">
-        <v>-0.05454545454545445</v>
+        <v>-1.451461001345933</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.280167286212716</v>
+        <v>306587.8787878789</v>
       </c>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
-        <v>1.849634088084997</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>154727.8538874348</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>-0.7974025974026517</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>-0.17316017316017</v>
-      </c>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="n">
-        <v>881725.1082251081</v>
-      </c>
+        <v>-1.401362243894255</v>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="n">
+        <v>2.245858585858585</v>
+      </c>
+      <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="n">
         <v>0</v>
       </c>
@@ -1606,32 +1608,32 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KEflYcbt</t>
+          <t>htYUpyrn</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45542.85416666666</v>
+        <v>45549.89583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">dickerson j 
+          <t xml:space="preserve">demianchuk s 
   usa </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">gillette stadium
-  foxborough  ma </t>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1658,117 +1660,2482 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>rXawJi8t</t>
+          <t>WSL0wFD4</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2PIEeC7j</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-1</v>
+      </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.833333333333334</v>
+        <v>3</v>
       </c>
       <c r="W7" t="n">
-        <v>-4.5</v>
+        <v>-3</v>
       </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>-0.1666666666666666</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>23.5</v>
+        <v>-1</v>
       </c>
       <c r="AC7" t="n">
-        <v>-23.5</v>
+        <v>4</v>
       </c>
       <c r="AD7" t="n">
-        <v>-5.166666666666668</v>
+        <v>-11</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.5</v>
+        <v>9</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.5</v>
+        <v>-5</v>
       </c>
       <c r="AG7" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="n">
-        <v>-0.6666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.3333333333333335</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>67.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="AM7" t="n">
-        <v>68.68181818181817</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>2.427349828820422</v>
-      </c>
+        <v>68.40000000000001</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
+      <c r="AP7" t="n">
+        <v>0.6930976430976443</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.203367003367021</v>
+      </c>
       <c r="AR7" t="n">
-        <v>3.553937130407725</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0.0553376906318086</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
+        <v>-328920.3861369109</v>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>1.56936026936026</v>
+      </c>
       <c r="AU7" t="n">
-        <v>1.199663299663303</v>
+        <v>0.1915824915824917</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.4692340067340126</v>
-      </c>
-      <c r="AW7" t="inlineStr"/>
+        <v>-1.535752678264288</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-2.001860963683733</v>
+      </c>
       <c r="AX7" t="n">
-        <v>-0.1590067340067343</v>
+        <v>-0.5660241289498202</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.521000622471206</v>
+        <v>763083.3333333335</v>
       </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
-        <v>-0.7374649859943929</v>
+        <v>0.01960784313725483</v>
       </c>
       <c r="BB7" t="n">
-        <v>144882.8976034857</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>-1.486910774410717</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0.575799663299648</v>
-      </c>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="n">
-        <v>-220851.2205387203</v>
-      </c>
+        <v>4.295611270824111</v>
+      </c>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="n">
+        <v>0.04831649831649543</v>
+      </c>
+      <c r="BF7" t="inlineStr"/>
       <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>dKkDSgSH</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chase stadium
+  fort lauderdale  fl </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>167</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>8.333333333333336</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-8.333333333333336</v>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-3.666666666666667</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-5.333333333333334</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>68.38787878787879</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="n">
+        <v>2.631363636363631</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.2445454545454879</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1040922.98085901</v>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>-0.09363636363636374</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.3509090909090908</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-1.708169934640523</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.927307422969193</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>4.867264239028941</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1406750</v>
+      </c>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="n">
+        <v>-0.04896708683473383</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.2470016339869403</v>
+      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="n">
+        <v>-1.727727272727265</v>
+      </c>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>A3m1Vera</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>167</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>63fk89be</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>65.63333333333333</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>70.43636363636364</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="n">
+        <v>0.0393939393939462</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-3.680303030303008</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>581690.4311209609</v>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>-1.077272727272742</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-0.06060606060606077</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-1.467625906197721</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.952497585609386</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>4.817737852196558</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-1666128.787878788</v>
+      </c>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="n">
+        <v>-0.01449275362318825</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-3.89940575009561</v>
+      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="n">
+        <v>-0.2742424242424271</v>
+      </c>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8lOY3V6E</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">da silva a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>167</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>67.77272727272728</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>67.12727272727273</v>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="n">
+        <v>-0.3165656565656718</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-1.050707070707119</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-377497.4234441016</v>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>-2.032929292929296</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.07454545454545469</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-1.756971174157201</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.5812171529731103</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.340272341514094</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-744575.7575757576</v>
+      </c>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="n">
+        <v>0.08704146730462514</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-4.627701854613264</v>
+      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="n">
+        <v>-2.583838383838383</v>
+      </c>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ITj9TZCB</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>167</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>-5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-4.666666666666664</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4.666666666666664</v>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>5.333333333333334</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>6.333333333333334</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>68.62424242424242</v>
+      </c>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="n">
+        <v>-2.984595959595964</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.6714646464646421</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-415930.7325801132</v>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>1.234090909090909</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.07828282828282851</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.2611772579845315</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-1.143372966172123</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-1.882497904185598</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-228895.2020202023</v>
+      </c>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="n">
+        <v>-0.08614114832535869</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>3.032860612426759</v>
+      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="n">
+        <v>4.296969696969693</v>
+      </c>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>lfn5UFc5</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>167</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>66.44949494949495</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>69.11363636363637</v>
+      </c>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="n">
+        <v>0.6420202020202055</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.3294949494949435</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-136760.9908207734</v>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="n">
+        <v>-0.488484848484859</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.1474815040032418</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-3.07253489264361</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-3.860379656575304</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-805216.1616161619</v>
+      </c>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.50050004343484</v>
+      </c>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="n">
+        <v>-1.296969696969693</v>
+      </c>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vquIRDsO</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bazakos f 
+  usa </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>167</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7.833333333333336</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-7.833333333333336</v>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-1.833333333333333</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-5.166666666666667</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>5.833333333333334</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.666666666666666</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>67.48989898989899</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>67.54107744107745</v>
+      </c>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="n">
+        <v>1.766666666666652</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-1.622222222222263</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1911779.472658628</v>
+      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="n">
+        <v>2.6111111111111</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-0.02444444444444427</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.6070401493930824</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.302283522104474</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.1082109365485167</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>653833.3333333333</v>
+      </c>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="n">
+        <v>0.2901786221735072</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0.4527406324848755</v>
+      </c>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="n">
+        <v>-0.3599999999999959</v>
+      </c>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>jDDw3kMK</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo field
+  toronto  on </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>167</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>67.63636363636364</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>67.55</v>
+      </c>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="n">
+        <v>0.7428282828282704</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0.4238383838383868</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>614032.9976786494</v>
+      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="n">
+        <v>0.1957575757575825</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.05494949494949486</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-4.073922140661274</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-2.722940742832044</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.7144386410690657</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>447804.0404040399</v>
+      </c>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="n">
+        <v>0.003824424367902424</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.914720653742364</v>
+      </c>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="n">
+        <v>-0.5391919191919214</v>
+      </c>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>trWntSE7</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45542.97916666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>167</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.1666666666666643</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.1666666666666643</v>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-4.333333333333332</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-2.333333333333334</v>
+      </c>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>66.25909090909092</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>67.14478114478113</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-2000000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>2.968001443001455</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-5.479148629148597</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-827402.6495557653</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-78</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.543217893217886</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-0.05584415584415603</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-0.07819192686435628</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.9351246604321091</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.3588960173210296</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1194107.142857143</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-64</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-0.03521181199752621</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-1.923289169006495</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>-0.6007575757575765</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45542.89583333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzales g 
+  usa </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>167</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>30</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-30</v>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>65.95</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>69.67777777777778</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-2400000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-2.9821212121212</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0.7930303030303492</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-999690.6163600539</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>-141</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>-3.803030303030297</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-0.1951515151515151</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.4420414794072123</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>-2.208832117016257</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-5.22092921287296</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>-1998715.151515152</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-131</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>-0.05595238095238098</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-1.570660266133416</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>-1.370303030303035</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>SvbdWyTh</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45542.89583333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bazakos f 
+  usa </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>167</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>9</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>68.26666666666667</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>65.06060606060606</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-1275000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.402525252525251</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-0.2090909090909179</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>111514.491618539</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>-154</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.210101010101013</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-0.009595959595959602</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.886491591297087</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2.387739616250784</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-0.9843477579818938</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1000227.272727273</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-0.006213450292397615</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>-2.092488354037272</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>-1.150505050505043</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>hIoLKAg0</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45542.85416666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>167</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-17.75</v>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-6.75</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>67.39204545454545</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>68.5060606060606</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="n">
+        <v>-0.4745959595959732</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>2.178571428571473</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-465626.5609390605</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>63</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-1.23945165945166</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>-0.1738095238095236</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-0.7000877638985017</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>-1.31548879509235</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>-1.537052142231161</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>777626.6233766228</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>63</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>-0.1883312020460359</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.720382005036754</v>
+      </c>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="n">
+        <v>-1.025721500721506</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>KEflYcbt</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45542.85416666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>167</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-23.5</v>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-5.166666666666668</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-1.833333333333334</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>68.45757575757575</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>5525000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0.01084175084176309</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>-1.149932659932603</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>304635.3278630294</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>-62</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.2468013468013623</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>-0.1271380471380474</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.993494448504045</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>3.232414088823951</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>2.02537840498519</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-221015.1515151516</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>-54</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.05418868996874115</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>-1.6858881886088</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.404410774410778</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>EyfhXHDn</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45542.85416666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">touchan r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>167</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>txm4BKVR</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.3333333333333357</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-0.3333333333333357</v>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.3333333333333339</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-1.666666666666666</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-5.333333333333333</v>
+      </c>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>67.63636363636364</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>-2975000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>4.666753246753245</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>-0.492207792207779</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>173528.0265056582</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>-146</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>-0.3070129870129961</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>-0.05194805194805197</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>-2.853811282157967</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>-1.016499227317311</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>3.160885638008054</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>838090.9090909089</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>-149</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>-0.08446115288220568</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.819385172417213</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>4.666666666666657</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>-7.666666666666668</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>-5.233506493506493</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BG20" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/usa/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/usa/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG20"/>
+  <dimension ref="A1:BG28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,94 +525,94 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions_against</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -625,97 +625,97 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_val_player_miss</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -727,11 +727,11 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>foKU4Bi8</t>
+          <t>YJuQfCBA</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45549.97916666666</v>
+        <v>45553.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -741,13 +741,13 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bc place
-  vancouver  bc </t>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>K2dlua5N</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>KtuTuMN0</t>
+          <t>zoZ995af</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -788,115 +788,115 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="Q2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.666666666666667</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6666666666666665</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
       <c r="W2" t="n">
-        <v>-6.5</v>
+        <v>-5</v>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.5</v>
+        <v>-0.1666666666666665</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1</v>
+        <v>-0.1666666666666665</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.5</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="AD2" t="n">
-        <v>-2.5</v>
+        <v>7.299999999999997</v>
       </c>
       <c r="AE2" t="n">
-        <v>-5.5</v>
+        <v>-7.299999999999997</v>
       </c>
       <c r="AF2" t="n">
-        <v>-2.5</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="AG2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="n">
-        <v>-0.1666666666666667</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-0.1666666666666667</v>
-      </c>
+        <v>-1.8</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>65.99081289081289</v>
+        <v>69.31464646464646</v>
       </c>
       <c r="AM2" t="n">
-        <v>65.47979797979798</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
+        <v>68.08888888888889</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.02619047619052139</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.3380952380952351</v>
+      </c>
       <c r="AP2" t="n">
-        <v>0.36944444444444</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-2.859090909090867</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-161485.4139218265</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="n">
-        <v>0.1474747474747318</v>
-      </c>
+        <v>0.8165873015873046</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>1312358.533157664</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>3.619717293505019</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1.091482213438734</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-0.7027964426877418</v>
-      </c>
+        <v>-405542.063492063</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>0.121998243302599</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-161568.1818181812</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
+        <v>-1.739903747006053</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="n">
+        <v>0.8030346984643586</v>
+      </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>-1.998705719969138</v>
       </c>
       <c r="BB2" t="n">
-        <v>-1.608271848924062</v>
+        <v>0.1615454877603215</v>
       </c>
       <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="n">
-        <v>-0.8689393939393959</v>
-      </c>
-      <c r="BF2" t="inlineStr"/>
+      <c r="BD2" t="n">
+        <v>0.3821428571428562</v>
+      </c>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="n">
+        <v>0.1753968253968254</v>
+      </c>
       <c r="BG2" t="n">
         <v>0</v>
       </c>
@@ -904,32 +904,32 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>l8RwqFCb</t>
+          <t>GroLehd4</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45549.97916666666</v>
+        <v>45553.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">villarreal a 
+          <t xml:space="preserve">dickerson j 
   usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">dignity health sports park
-  carson  ca </t>
+          <t xml:space="preserve">providence park
+  portland  or </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>U3ebh62R</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -956,124 +956,124 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>WSL0wFD4</t>
+          <t>EqKWmJfM</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>86yPt28f</t>
+          <t>2PIEeC7j</t>
         </is>
       </c>
       <c r="O3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="U3" t="n">
         <v>1</v>
       </c>
-      <c r="P3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
       <c r="V3" t="n">
-        <v>11.83333333333334</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-11.83333333333334</v>
+        <v>6</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.6666666666666665</v>
+        <v>-1</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.5</v>
+        <v>-0.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>-6.333333333333334</v>
+        <v>-3.666666666666671</v>
       </c>
       <c r="AE3" t="n">
-        <v>-3.666666666666666</v>
+        <v>3.666666666666671</v>
       </c>
       <c r="AF3" t="n">
-        <v>5.833333333333334</v>
+        <v>1.333333333333334</v>
       </c>
       <c r="AG3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="n">
-        <v>0.6666666666666665</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
+        <v>1.666666666666666</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>3.333333333333334</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>67.02592592592593</v>
+        <v>68.42468434343434</v>
       </c>
       <c r="AM3" t="n">
-        <v>69.303367003367</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
+        <v>69.55416666666666</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-0.07318181818186531</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>-1.125454545454545</v>
+      </c>
       <c r="AP3" t="n">
-        <v>-0.5393939393939178</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-2.901515151515071</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-195358.7662803028</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="n">
-        <v>-1.724242424242419</v>
-      </c>
+        <v>-2.049090909090921</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="n">
+        <v>-338630.5448857658</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
-        <v>-0.3212121212121213</v>
+        <v>0.09480517416730549</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.5869834363835906</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-2.645087391681813</v>
-      </c>
+        <v>-1602545.454545455</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>-3.575608910496683</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-126818.1818181821</v>
-      </c>
-      <c r="AZ3" t="inlineStr"/>
+        <v>0.6194646489411895</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="n">
+        <v>2.119187461407137</v>
+      </c>
       <c r="BA3" t="n">
-        <v>0.04910192147034254</v>
+        <v>1.188219983836376</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.4651770543411544</v>
+        <v>-0.1260651629072682</v>
       </c>
       <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="n">
-        <v>-2.169696969696972</v>
-      </c>
-      <c r="BF3" t="inlineStr"/>
+      <c r="BD3" t="n">
+        <v>0.4190909090909045</v>
+      </c>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="n">
+        <v>-0.06000000000000005</v>
+      </c>
       <c r="BG3" t="n">
         <v>0</v>
       </c>
@@ -1081,32 +1081,32 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AHSZqech</t>
+          <t>xhnHdYtb</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45549.9375</v>
+        <v>45553.97916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">szpala l 
+          <t xml:space="preserve">allatin m 
   usa </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">dick s sporting goods park
-  commerce city  co </t>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>bm8usLzB</t>
+          <t>IeT6JBE3</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1133,22 +1133,22 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>WWvwigh8</t>
+          <t>86yPt28f</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>tOpyQa24</t>
+          <t>Sd7snoa0</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -1157,100 +1157,100 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-12</v>
+        <v>0.25</v>
       </c>
       <c r="W4" t="n">
-        <v>12</v>
+        <v>2.75</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>1</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1</v>
+        <v>0.4666666666666663</v>
       </c>
       <c r="AB4" t="n">
-        <v>-2</v>
+        <v>0.2666666666666668</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AD4" t="n">
-        <v>-3</v>
+        <v>-8.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>-0.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>-3</v>
-      </c>
+        <v>-3.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-7.25</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>65.72727272727273</v>
+        <v>69.32711111111112</v>
       </c>
       <c r="AM4" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
+        <v>68.26262626262627</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-0.4867676767676414</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>5.506363636363631</v>
+      </c>
       <c r="AP4" t="n">
-        <v>-1.974949494949499</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>2.230101010101009</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>-870581.7193675886</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="n">
-        <v>-4.219191919191914</v>
-      </c>
+        <v>5.87808080808081</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>689177.8920000144</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>5.663232249421497</v>
       </c>
       <c r="AV4" t="n">
-        <v>-4.098359683794463</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>-8.343504611330687</v>
-      </c>
+        <v>1796946.96969697</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>-1.317490118577084</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>-784008.0808080807</v>
-      </c>
-      <c r="AZ4" t="inlineStr"/>
+        <v>-3.732068732631394</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="n">
+        <v>-0.03660787635210738</v>
+      </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>-0.3255592460963612</v>
       </c>
       <c r="BB4" t="n">
-        <v>-1.043474967061911</v>
+        <v>-0.1345413764978982</v>
       </c>
       <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="n">
-        <v>-2.376161616161614</v>
-      </c>
-      <c r="BF4" t="inlineStr"/>
+      <c r="BD4" t="n">
+        <v>0.8381818181818161</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="n">
+        <v>0.1925252525252528</v>
+      </c>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
@@ -1258,32 +1258,32 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xUcLQXdU</t>
+          <t>rVnDcERi</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45549.89583333334</v>
+        <v>45553.9375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">marrufo j 
+          <t xml:space="preserve">chapman a 
   usa </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">soldier field
-  chicago  il </t>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1310,120 +1310,124 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>6LuGZiZI</t>
+          <t>rXawJi8t</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>6BusaLE3</t>
+          <t>WWvwigh8</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>12</v>
+        <v>-11</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Q5" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
       <c r="V5" t="n">
-        <v>4</v>
+        <v>5.666666666666668</v>
       </c>
       <c r="W5" t="n">
-        <v>-4</v>
+        <v>-4.333333333333334</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AC5" t="n">
-        <v>4</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AD5" t="n">
-        <v>6</v>
+        <v>1.333333333333329</v>
       </c>
       <c r="AE5" t="n">
-        <v>5</v>
+        <v>-1.333333333333329</v>
       </c>
       <c r="AF5" t="n">
-        <v>-5</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="AG5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1</v>
-      </c>
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>3.333333333333334</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>69.26010101010101</v>
+        <v>67.53775252525253</v>
       </c>
       <c r="AM5" t="n">
-        <v>69.45454545454545</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
+        <v>65.55892255892256</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-2.239696969697007</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.1062626262626196</v>
+      </c>
       <c r="AP5" t="n">
-        <v>-1.738181818181829</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>2.548484848484833</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-169856.8220823801</v>
-      </c>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="n">
-        <v>2.850303030303039</v>
-      </c>
+        <v>2.958585858585849</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>-1092063.242972628</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>0.09090909090909105</v>
+        <v>-0.4645370165609961</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.519433320620397</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.8477599796593012</v>
-      </c>
+        <v>-136477.2727272727</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>-2.031821128909215</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>326151.5151515156</v>
-      </c>
-      <c r="AZ5" t="inlineStr"/>
+        <v>1.89205347928646</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="n">
+        <v>1.706789891395147</v>
+      </c>
       <c r="BA5" t="n">
-        <v>0.00694444444444442</v>
+        <v>-0.6096770725833949</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.487123379099927</v>
+        <v>-0.01835317460317465</v>
       </c>
       <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="n">
-        <v>3.997575757575763</v>
-      </c>
-      <c r="BF5" t="inlineStr"/>
+      <c r="BD5" t="n">
+        <v>-1.552525252525257</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="n">
+        <v>-0.06515151515151518</v>
+      </c>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
@@ -1431,11 +1435,11 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EkZQoHSu</t>
+          <t>URr9bfCo</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45549.89583333334</v>
+        <v>45553.89583333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1445,18 +1449,18 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">shell energy stadium
-  houston  tx </t>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>84yIDQMe</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1483,124 +1487,124 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>UL7r7duf</t>
+          <t>K4zRMgTN</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>GzULyFoh</t>
+          <t>nJ01AhXP</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" t="n">
-        <v>11</v>
-      </c>
-      <c r="R6" t="n">
-        <v>3</v>
-      </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5</v>
+        <v>-0.1666666666666665</v>
       </c>
       <c r="V6" t="n">
-        <v>15</v>
+        <v>2.166666666666666</v>
       </c>
       <c r="W6" t="n">
-        <v>-15</v>
+        <v>2.5</v>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>-1.5</v>
+        <v>-0.5833333333333335</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1</v>
+        <v>-0.08333333333333348</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.5</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.5</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="AD6" t="n">
         <v>-3.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>4.333333333333334</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>70.32878787878788</v>
+        <v>68.17676767676768</v>
       </c>
       <c r="AM6" t="n">
-        <v>69.33333333333334</v>
-      </c>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
+        <v>67.95681818181818</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.4769696969697179</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0.3393939393939291</v>
+      </c>
       <c r="AP6" t="n">
-        <v>-0.3907070707070659</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.920606060606076</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>-353229.0914470581</v>
-      </c>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="n">
-        <v>2.217979797979808</v>
-      </c>
+        <v>-2.212727272727278</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>-392191.8218927542</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="n">
-        <v>0.1927272727272729</v>
+        <v>-3.333213885096384</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.8755639870217884</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>-0.8768246473617154</v>
-      </c>
+        <v>671727.2727272725</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="n">
-        <v>-1.451461001345933</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>306587.8787878789</v>
-      </c>
-      <c r="AZ6" t="inlineStr"/>
+        <v>1.983181979885771</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>-0.9815233095526494</v>
+      </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>2.503630639898972</v>
       </c>
       <c r="BB6" t="n">
-        <v>-1.401362243894255</v>
+        <v>-0.01488095238095233</v>
       </c>
       <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="n">
-        <v>2.245858585858585</v>
-      </c>
-      <c r="BF6" t="inlineStr"/>
+      <c r="BD6" t="n">
+        <v>1.459999999999997</v>
+      </c>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="n">
+        <v>0.04000000000000004</v>
+      </c>
       <c r="BG6" t="n">
         <v>0</v>
       </c>
@@ -1608,32 +1612,32 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>htYUpyrn</t>
+          <t>0n3Ddmal</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45549.89583333334</v>
+        <v>45553.89583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">demianchuk s 
+          <t xml:space="preserve">chapman a 
   usa </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">citypark
-  st  louis  mo </t>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1660,124 +1664,124 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>WSL0wFD4</t>
+          <t>86yPt28f</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>UFWZoX9L</t>
+          <t>WWvwigh8</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="V7" t="n">
-        <v>3</v>
+        <v>4.833333333333334</v>
       </c>
       <c r="W7" t="n">
-        <v>-3</v>
+        <v>-2.5</v>
       </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>0.5499999999999998</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>-0.1499999999999999</v>
       </c>
       <c r="AB7" t="n">
-        <v>-1</v>
+        <v>0.3500000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>4</v>
+        <v>-0.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>-11</v>
+        <v>17.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>9</v>
+        <v>-17.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>-5</v>
+        <v>-0.166666666666667</v>
       </c>
       <c r="AG7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-0.6666666666666661</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>71.40000000000001</v>
+        <v>69.8909494949495</v>
       </c>
       <c r="AM7" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
+        <v>68.33712121212122</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>3.993939393939399</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.03989898989898677</v>
+      </c>
       <c r="AP7" t="n">
-        <v>0.6930976430976443</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.203367003367021</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-328920.3861369109</v>
-      </c>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="n">
-        <v>1.56936026936026</v>
-      </c>
+        <v>-0.09131313131312879</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="n">
+        <v>-132973.5430691314</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="n">
-        <v>0.1915824915824917</v>
+        <v>-0.7638446525530753</v>
       </c>
       <c r="AV7" t="n">
-        <v>-1.535752678264288</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>-2.001860963683733</v>
-      </c>
+        <v>-489212.1212121216</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="n">
-        <v>-0.5660241289498202</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>763083.3333333335</v>
-      </c>
-      <c r="AZ7" t="inlineStr"/>
+        <v>-0.12251230677062</v>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="n">
+        <v>-0.1849149912321337</v>
+      </c>
       <c r="BA7" t="n">
-        <v>0.01960784313725483</v>
+        <v>-1.090008407335802</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.295611270824111</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="n">
-        <v>0.04831649831649543</v>
-      </c>
-      <c r="BF7" t="inlineStr"/>
+      <c r="BD7" t="n">
+        <v>1.90424242424243</v>
+      </c>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="n">
+        <v>0.1939393939393941</v>
+      </c>
       <c r="BG7" t="n">
         <v>0</v>
       </c>
@@ -1785,32 +1789,32 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dKkDSgSH</t>
+          <t>SM4QZAZp</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45553.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">marrufo j 
+          <t xml:space="preserve">freemon j 
   usa </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">chase stadium
-  fort lauderdale  fl </t>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0AheRyBg</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1837,25 +1841,25 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>6LuGZiZI</t>
+          <t>bFuhdIb3</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>6BusaLE3</t>
+          <t>K4FYmLD9</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1864,97 +1868,97 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="V8" t="n">
-        <v>8.333333333333336</v>
+        <v>0.3333333333333321</v>
       </c>
       <c r="W8" t="n">
-        <v>-8.333333333333336</v>
+        <v>-5.833333333333334</v>
       </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>0.3333333333333335</v>
+        <v>-0.4166666666666665</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6666666666666666</v>
+        <v>-0.1666666666666665</v>
       </c>
       <c r="AB8" t="n">
-        <v>-3</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>-8.666666666666664</v>
       </c>
       <c r="AE8" t="n">
-        <v>12</v>
+        <v>8.666666666666664</v>
       </c>
       <c r="AF8" t="n">
-        <v>-3.666666666666667</v>
+        <v>-2.833333333333333</v>
       </c>
       <c r="AG8" t="n">
-        <v>-5.333333333333334</v>
-      </c>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.6666666666666661</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>68.38787878787879</v>
+        <v>68.89974747474747</v>
       </c>
       <c r="AM8" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
+        <v>68.5986531986532</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-0.4527272727272873</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-1.912727272727253</v>
+      </c>
       <c r="AP8" t="n">
-        <v>2.631363636363631</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0.2445454545454879</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1040922.98085901</v>
-      </c>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="n">
-        <v>-0.09363636363636374</v>
-      </c>
+        <v>-2.261818181818185</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="n">
+        <v>-713686.4567909543</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="n">
-        <v>0.3509090909090908</v>
+        <v>1.822139027235608</v>
       </c>
       <c r="AV8" t="n">
-        <v>-1.708169934640523</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.927307422969193</v>
-      </c>
+        <v>-1112145.454545454</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="n">
-        <v>4.867264239028941</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1406750</v>
-      </c>
-      <c r="AZ8" t="inlineStr"/>
+        <v>1.051832907075877</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="n">
+        <v>2.156005743258397</v>
+      </c>
       <c r="BA8" t="n">
-        <v>-0.04896708683473383</v>
+        <v>-3.067805222775604</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.2470016339869403</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="n">
-        <v>-1.727727272727265</v>
-      </c>
-      <c r="BF8" t="inlineStr"/>
+      <c r="BD8" t="n">
+        <v>0.7745454545454571</v>
+      </c>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
       <c r="BG8" t="n">
         <v>0</v>
       </c>
@@ -1962,32 +1966,32 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>A3m1Vera</t>
+          <t>QDIbviRT</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45553.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">rivas v 
-  usa </t>
+          <t xml:space="preserve">montero r 
+  cos </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">mercedes benz stadium
-  atlanta  ga </t>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2014,124 +2018,124 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>022mBmSn</t>
+          <t>KIxd2dNg</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>63fk89be</t>
+          <t>lAVQ9RGh</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="Q9" t="n">
+        <v>15</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="V9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-12.5</v>
-      </c>
       <c r="W9" t="n">
-        <v>12.5</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>2</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="AA9" t="n">
-        <v>-1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>6</v>
+        <v>-0.5333333333333334</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.5</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="AD9" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-17.75</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AH9" t="n">
         <v>-1</v>
       </c>
-      <c r="AE9" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>-2.5</v>
-      </c>
+      <c r="AI9" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>65.63333333333333</v>
+        <v>67.54361471861472</v>
       </c>
       <c r="AM9" t="n">
-        <v>70.43636363636364</v>
-      </c>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
+        <v>66.89393939393939</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.079040404040398</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1.322474747474743</v>
+      </c>
       <c r="AP9" t="n">
-        <v>0.0393939393939462</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>-3.680303030303008</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>581690.4311209609</v>
-      </c>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="n">
-        <v>-1.077272727272742</v>
-      </c>
+        <v>-1.12904040404041</v>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>415954.0239350023</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
       <c r="AU9" t="n">
-        <v>-0.06060606060606077</v>
+        <v>-0.6063076416337196</v>
       </c>
       <c r="AV9" t="n">
-        <v>-1.467625906197721</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.952497585609386</v>
-      </c>
+        <v>-118811.8686868686</v>
+      </c>
+      <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="n">
-        <v>4.817737852196558</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>-1666128.787878788</v>
-      </c>
-      <c r="AZ9" t="inlineStr"/>
+        <v>4.84199055775143</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="n">
+        <v>5.766304347826086</v>
+      </c>
       <c r="BA9" t="n">
-        <v>-0.01449275362318825</v>
+        <v>-0.987329819938509</v>
       </c>
       <c r="BB9" t="n">
-        <v>-3.89940575009561</v>
+        <v>0.06527777777777799</v>
       </c>
       <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="n">
-        <v>-0.2742424242424271</v>
-      </c>
-      <c r="BF9" t="inlineStr"/>
+      <c r="BD9" t="n">
+        <v>3.383080808080809</v>
+      </c>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="n">
+        <v>0.06060606060606055</v>
+      </c>
       <c r="BG9" t="n">
         <v>0</v>
       </c>
@@ -2139,11 +2143,11 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>8lOY3V6E</t>
+          <t>ImJfuXBN</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45553.88541666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2153,13 +2157,13 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">saputo stadium
-  montreal  qc </t>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2191,7 +2195,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>roEEsq76</t>
+          <t>K4zRMgTN</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2200,16 +2204,16 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2218,97 +2222,97 @@
         <v>0.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="V10" t="n">
-        <v>21.5</v>
+        <v>4.833333333333334</v>
       </c>
       <c r="W10" t="n">
-        <v>-21.5</v>
+        <v>5.5</v>
       </c>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>-1.5</v>
+        <v>0.4166666666666665</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>-3.5</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.5</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>4.666666666666664</v>
       </c>
       <c r="AE10" t="n">
-        <v>6.5</v>
+        <v>-4.666666666666664</v>
       </c>
       <c r="AF10" t="n">
-        <v>-4.5</v>
+        <v>-0.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2</v>
-      </c>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-6.166666666666668</v>
+      </c>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>67.77272727272728</v>
+        <v>67.29657687991022</v>
       </c>
       <c r="AM10" t="n">
-        <v>67.12727272727273</v>
-      </c>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
+        <v>66.50540404040404</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-1.003636363636389</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.545454545454547</v>
+      </c>
       <c r="AP10" t="n">
-        <v>-0.3165656565656718</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>-1.050707070707119</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>-377497.4234441016</v>
-      </c>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="n">
-        <v>-2.032929292929296</v>
-      </c>
+        <v>0.1145454545454498</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>1425312.109033337</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
       <c r="AU10" t="n">
-        <v>0.07454545454545469</v>
+        <v>0.5265054638456093</v>
       </c>
       <c r="AV10" t="n">
-        <v>-1.756971174157201</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0.5812171529731103</v>
-      </c>
+        <v>318500</v>
+      </c>
+      <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="n">
-        <v>1.340272341514094</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>-744575.7575757576</v>
-      </c>
-      <c r="AZ10" t="inlineStr"/>
+        <v>1.104131929451622</v>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="n">
+        <v>1.91618228318994</v>
+      </c>
       <c r="BA10" t="n">
-        <v>0.08704146730462514</v>
+        <v>-2.957697545421325</v>
       </c>
       <c r="BB10" t="n">
-        <v>-4.627701854613264</v>
+        <v>0.3639751552795032</v>
       </c>
       <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="n">
-        <v>-2.583838383838383</v>
-      </c>
-      <c r="BF10" t="inlineStr"/>
+      <c r="BD10" t="n">
+        <v>-0.1436363636363573</v>
+      </c>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="n">
+        <v>0.04000000000000004</v>
+      </c>
       <c r="BG10" t="n">
         <v>0</v>
       </c>
@@ -2316,32 +2320,32 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ITj9TZCB</t>
+          <t>dYUosgsB</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45553.85416666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">unkel t 
-  usa </t>
+          <t xml:space="preserve">lauziere p 
+  can </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>0AheRyBg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2368,120 +2372,124 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>xA45kovo</t>
+          <t>022mBmSn</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>dp6AQn9c</t>
+          <t>6gpXy3vi</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.3333333333333334</v>
+      </c>
       <c r="V11" t="n">
-        <v>-4.666666666666664</v>
+        <v>-3.333333333333334</v>
       </c>
       <c r="W11" t="n">
-        <v>4.666666666666664</v>
+        <v>-7.333333333333333</v>
       </c>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>1.333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.333333333333333</v>
+        <v>-0.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.666666666666667</v>
+        <v>0.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>5.333333333333334</v>
+        <v>-5.333333333333336</v>
       </c>
       <c r="AE11" t="n">
-        <v>-7</v>
+        <v>5.333333333333336</v>
       </c>
       <c r="AF11" t="n">
-        <v>6.333333333333334</v>
+        <v>-0.666666666666667</v>
       </c>
       <c r="AG11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="n">
-        <v>-0.6666666666666666</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.333333333333333</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>4.666666666666666</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>66.40000000000001</v>
+        <v>69.03409090909091</v>
       </c>
       <c r="AM11" t="n">
-        <v>68.62424242424242</v>
-      </c>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
+        <v>69.42681818181818</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-3.889999999999986</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-4.322727272727249</v>
+      </c>
       <c r="AP11" t="n">
-        <v>-2.984595959595964</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0.6714646464646421</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>-415930.7325801132</v>
-      </c>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="n">
-        <v>1.234090909090909</v>
-      </c>
+        <v>-7.369545454545445</v>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="n">
+        <v>-730111.4243943188</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
       <c r="AU11" t="n">
-        <v>0.07828282828282851</v>
+        <v>-5.000185881370101</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.2611772579845315</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>-1.143372966172123</v>
-      </c>
+        <v>-3261468.181818182</v>
+      </c>
+      <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="n">
-        <v>-1.882497904185598</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>-228895.2020202023</v>
-      </c>
-      <c r="AZ11" t="inlineStr"/>
+        <v>2.748404344193823</v>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="n">
+        <v>-1.64872493734336</v>
+      </c>
       <c r="BA11" t="n">
-        <v>-0.08614114832535869</v>
+        <v>-4.437356934001627</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.032860612426759</v>
+        <v>-0.05803571428571441</v>
       </c>
       <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="n">
-        <v>4.296969696969693</v>
-      </c>
-      <c r="BF11" t="inlineStr"/>
+      <c r="BD11" t="n">
+        <v>2.640454545454539</v>
+      </c>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="n">
+        <v>-0.3872727272727274</v>
+      </c>
       <c r="BG11" t="n">
         <v>0</v>
       </c>
@@ -2489,32 +2497,32 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>lfn5UFc5</t>
+          <t>U3Cs29yR</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45553.85416666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">unkel t 
+          <t xml:space="preserve">freemon j 
   usa </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">tql stadium
-  cincinnati  oh </t>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2541,22 +2549,22 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>roEEsq76</t>
+          <t>GzULyFoh</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>dp6AQn9c</t>
+          <t>K4FYmLD9</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2565,133 +2573,137 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-1</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5</v>
+        <v>-2.083333333333333</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>-4</v>
       </c>
       <c r="W12" t="n">
-        <v>-1.5</v>
+        <v>1.666666666666666</v>
       </c>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>1</v>
+        <v>0.5499999999999998</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>0.3500000000000001</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.5</v>
+        <v>0.95</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.5</v>
+        <v>-1.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.5</v>
+        <v>-0.6666666666666643</v>
       </c>
       <c r="AE12" t="n">
-        <v>6</v>
+        <v>0.6666666666666643</v>
       </c>
       <c r="AF12" t="n">
-        <v>6</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>4.083333333333333</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>4.75</v>
+      </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AL12" t="n">
-        <v>66.44949494949495</v>
+        <v>66.80828282828284</v>
       </c>
       <c r="AM12" t="n">
-        <v>69.11363636363637</v>
-      </c>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
+        <v>68.22499999999999</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.601885521885549</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1.213569023569022</v>
+      </c>
       <c r="AP12" t="n">
-        <v>0.6420202020202055</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0.3294949494949435</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>-136760.9908207734</v>
-      </c>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="n">
-        <v>-0.488484848484859</v>
-      </c>
+        <v>-1.077037037037016</v>
+      </c>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="n">
+        <v>-114542.0639582369</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>-1.263673506986876</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.1474815040032418</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>-3.07253489264361</v>
-      </c>
+        <v>675316.4983164982</v>
+      </c>
+      <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="n">
-        <v>-3.860379656575304</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>-805216.1616161619</v>
-      </c>
-      <c r="AZ12" t="inlineStr"/>
+        <v>2.561758051578348</v>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="n">
+        <v>0.241447288297465</v>
+      </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.914058355931388</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.50050004343484</v>
+        <v>-0.01363959447819996</v>
       </c>
       <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="n">
-        <v>-1.296969696969693</v>
-      </c>
-      <c r="BF12" t="inlineStr"/>
+      <c r="BD12" t="n">
+        <v>2.722053872053873</v>
+      </c>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="n">
+        <v>-0.002323232323232505</v>
+      </c>
       <c r="BG12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>vquIRDsO</t>
+          <t>vcKjtDdH</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45553.85416666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">bazakos f 
+          <t xml:space="preserve">marrufo j 
   usa </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">inter co stadium
-  orlando  fl </t>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>Szrwix67</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2718,40 +2730,40 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>K4zRMgTN</t>
+          <t>zoZ995af</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>GzULyFoh</t>
+          <t>6BusaLE3</t>
         </is>
       </c>
       <c r="O13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" t="n">
         <v>-3</v>
       </c>
-      <c r="P13" t="n">
-        <v>-1</v>
-      </c>
       <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
         <v>2</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.5</v>
-      </c>
       <c r="V13" t="n">
-        <v>7.833333333333336</v>
+        <v>1.666666666666666</v>
       </c>
       <c r="W13" t="n">
-        <v>-7.833333333333336</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
@@ -2759,99 +2771,99 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.833333333333333</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.666666666666667</v>
+        <v>-1</v>
       </c>
       <c r="AC13" t="n">
-        <v>-5.166666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AE13" t="n">
-        <v>5.833333333333334</v>
+        <v>-7</v>
       </c>
       <c r="AF13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-0.333333333333333</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.666666666666666</v>
       </c>
-      <c r="AG13" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="n">
+      <c r="AI13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="n">
+        <v>68.60267676767677</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>67.46174242424243</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-1.119343434343392</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-5.593888888888884</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0.75247474747475</v>
+      </c>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="n">
+        <v>143776.7501976867</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="n">
+        <v>1.606839733022383</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-1704089.646464646</v>
+      </c>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="n">
+        <v>-1.920501119107929</v>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="n">
+        <v>-1.30341892163564</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-3.432149183118156</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0.007703758058247523</v>
+      </c>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="n">
+        <v>-3.705252525252522</v>
+      </c>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="n">
+        <v>-0.1086868686868689</v>
+      </c>
+      <c r="BG13" t="n">
         <v>1</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>67.48989898989899</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>67.54107744107745</v>
-      </c>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="n">
-        <v>1.766666666666652</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>-1.622222222222263</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1911779.472658628</v>
-      </c>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="n">
-        <v>2.6111111111111</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>-0.02444444444444427</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0.6070401493930824</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.302283522104474</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0.1082109365485167</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>653833.3333333333</v>
-      </c>
-      <c r="AZ13" t="inlineStr"/>
-      <c r="BA13" t="n">
-        <v>0.2901786221735072</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>-0.4527406324848755</v>
-      </c>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="n">
-        <v>-0.3599999999999959</v>
-      </c>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>jDDw3kMK</t>
+          <t>Me49cTqr</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45553.85416666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">allatin m 
+          <t xml:space="preserve">mendoza r 
   usa </t>
         </is>
       </c>
@@ -2868,7 +2880,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2900,115 +2912,119 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Sd7snoa0</t>
+          <t>tOpyQa24</t>
         </is>
       </c>
       <c r="O14" t="n">
+        <v>-7</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
         <v>-1</v>
       </c>
-      <c r="P14" t="n">
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U14" t="n">
         <v>-1</v>
       </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-2</v>
-      </c>
       <c r="V14" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="W14" t="n">
-        <v>-8.5</v>
+        <v>-0.9166666666666661</v>
       </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>-0.5</v>
+        <v>-0.5499999999999998</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.5</v>
+        <v>-0.7999999999999998</v>
       </c>
       <c r="AB14" t="n">
-        <v>-3</v>
+        <v>0.3500000000000001</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.5</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>-13.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>-6</v>
+        <v>13.25</v>
       </c>
       <c r="AF14" t="n">
-        <v>-8.5</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="AG14" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.5</v>
-      </c>
+        <v>-1.583333333333333</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-5.916666666666667</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0.8333333333333339</v>
+      </c>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
-        <v>67.63636363636364</v>
+        <v>67.36166666666666</v>
       </c>
       <c r="AM14" t="n">
-        <v>67.55</v>
-      </c>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
+        <v>68.13867676767677</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-0.2934680134680434</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.509090909090915</v>
+      </c>
       <c r="AP14" t="n">
-        <v>0.7428282828282704</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>-0.4238383838383868</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>614032.9976786494</v>
-      </c>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="n">
-        <v>0.1957575757575825</v>
-      </c>
+        <v>-2.531212121212135</v>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="n">
+        <v>-272483.9084526589</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
       <c r="AU14" t="n">
-        <v>0.05494949494949486</v>
+        <v>-2.762187812187832</v>
       </c>
       <c r="AV14" t="n">
-        <v>-4.073922140661274</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>-2.722940742832044</v>
-      </c>
+        <v>-462808.7542087543</v>
+      </c>
+      <c r="AW14" t="inlineStr"/>
       <c r="AX14" t="n">
-        <v>0.7144386410690657</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>447804.0404040399</v>
-      </c>
-      <c r="AZ14" t="inlineStr"/>
+        <v>-0.1646485458985474</v>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="n">
+        <v>-1.885764929514941</v>
+      </c>
       <c r="BA14" t="n">
-        <v>0.003824424367902424</v>
+        <v>1.830382117882095</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.914720653742364</v>
+        <v>0.1943181818181816</v>
       </c>
       <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="n">
-        <v>-0.5391919191919214</v>
-      </c>
-      <c r="BF14" t="inlineStr"/>
+      <c r="BD14" t="n">
+        <v>1.85225589225589</v>
+      </c>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="n">
+        <v>0.2593939393939393</v>
+      </c>
       <c r="BG14" t="n">
         <v>0</v>
       </c>
@@ -3016,32 +3032,32 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>trWntSE7</t>
+          <t>rVQsrZR4</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45542.97916666666</v>
+        <v>45550.84375</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapman a 
+          <t xml:space="preserve">touchan r 
   usa </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">bc place
-  vancouver  bc </t>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>K2dlua5N</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3068,40 +3084,40 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>KtuTuMN0</t>
+          <t>zoZ995af</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>lAVQ9RGh</t>
+          <t>jBBpU7Y0</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-1</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0.3666666666666667</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1666666666666643</v>
+        <v>0.4333333333333336</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.1666666666666643</v>
+        <v>0.5333333333333332</v>
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
@@ -3109,96 +3125,86 @@
         <v>0.5</v>
       </c>
       <c r="AA15" t="n">
+        <v>-0.7666666666666666</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="AC15" t="n">
         <v>0.5</v>
       </c>
-      <c r="AB15" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC15" t="n">
+      <c r="AD15" t="n">
+        <v>0.7666666666666657</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.7666666666666657</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.8666666666666671</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1</v>
       </c>
-      <c r="AD15" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>-4.333333333333332</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>-2.333333333333334</v>
-      </c>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
+      <c r="AI15" t="n">
+        <v>3.233333333333334</v>
+      </c>
       <c r="AJ15" t="n">
-        <v>0.1666666666666667</v>
+        <v>10</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.1666666666666667</v>
+        <v>5</v>
       </c>
       <c r="AL15" t="n">
-        <v>66.25909090909092</v>
+        <v>69.49747474747475</v>
       </c>
       <c r="AM15" t="n">
-        <v>67.14478114478113</v>
+        <v>67.50909090909092</v>
       </c>
       <c r="AN15" t="n">
-        <v>-2000000</v>
+        <v>-1.322294372294351</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>2.835064935064935</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.968001443001455</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>-5.479148629148597</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>-827402.6495557653</v>
-      </c>
+        <v>3.758405483405483</v>
+      </c>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
       <c r="AS15" t="n">
-        <v>-78</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>3.543217893217886</v>
-      </c>
+        <v>1627445.075757576</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
       <c r="AU15" t="n">
-        <v>-0.05584415584415603</v>
+        <v>5.014132972029387</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.07819192686435628</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0.9351246604321091</v>
-      </c>
+        <v>1377000.360750361</v>
+      </c>
+      <c r="AW15" t="inlineStr"/>
       <c r="AX15" t="n">
-        <v>0.3588960173210296</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1194107.142857143</v>
-      </c>
+        <v>-1.753680207260775</v>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="n">
-        <v>-64</v>
+        <v>2.2164727748807</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0.03521181199752621</v>
+        <v>-1.374664437580037</v>
       </c>
       <c r="BB15" t="n">
-        <v>-1.923289169006495</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>-4.5</v>
-      </c>
+        <v>0.09626770998254353</v>
+      </c>
+      <c r="BC15" t="inlineStr"/>
       <c r="BD15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>-0.6007575757575765</v>
-      </c>
+        <v>-1.114826839826843</v>
+      </c>
+      <c r="BE15" t="inlineStr"/>
       <c r="BF15" t="n">
-        <v>-1</v>
+        <v>0.1147907647907649</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3207,11 +3213,11 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>AoWGqXpJ</t>
+          <t>l8RwqFCb</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45542.89583333334</v>
+        <v>45549.97916666666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -3221,13 +3227,13 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">shell energy stadium
-  houston  tx </t>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3259,137 +3265,123 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
+          <t>WSL0wFD4</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>UL7r7duf</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>86yPt28f</t>
-        </is>
-      </c>
       <c r="O16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.9</v>
+      </c>
       <c r="V16" t="n">
-        <v>30</v>
+        <v>-1.9</v>
       </c>
       <c r="W16" t="n">
-        <v>-30</v>
+        <v>-5.35</v>
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
-        <v>-1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1</v>
+        <v>-0.9500000000000002</v>
       </c>
       <c r="AB16" t="n">
-        <v>3</v>
+        <v>0.6499999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>-4.5</v>
+        <v>12.65</v>
       </c>
       <c r="AE16" t="n">
-        <v>-3</v>
+        <v>-12.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>13</v>
+        <v>3.9</v>
       </c>
       <c r="AG16" t="n">
-        <v>-9</v>
+        <v>0.9500000000000002</v>
       </c>
       <c r="AH16" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="AI16" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>2</v>
-      </c>
+        <v>-5.300000000000001</v>
+      </c>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="n">
-        <v>65.95</v>
+        <v>67.61035353535354</v>
       </c>
       <c r="AM16" t="n">
-        <v>69.67777777777778</v>
+        <v>68.57111111111112</v>
       </c>
       <c r="AN16" t="n">
-        <v>-2400000</v>
+        <v>-3.21545454545452</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>-2.073030303030308</v>
       </c>
       <c r="AP16" t="n">
-        <v>-2.9821212121212</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0.7930303030303492</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>-999690.6163600539</v>
-      </c>
+        <v>-0.3069696969696878</v>
+      </c>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
-        <v>-141</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>-3.803030303030297</v>
-      </c>
+        <v>-93135.61449300568</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
       <c r="AU16" t="n">
-        <v>-0.1951515151515151</v>
+        <v>-3.710290152743696</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.4420414794072123</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>-2.208832117016257</v>
-      </c>
+        <v>-42113.6363636367</v>
+      </c>
+      <c r="AW16" t="inlineStr"/>
       <c r="AX16" t="n">
-        <v>-5.22092921287296</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>-1998715.151515152</v>
-      </c>
+        <v>0.2653017905726891</v>
+      </c>
+      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="n">
-        <v>-131</v>
+        <v>-1.793486166396391</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0.05595238095238098</v>
+        <v>0.6309260227216953</v>
       </c>
       <c r="BB16" t="n">
-        <v>-1.570660266133416</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>-5</v>
-      </c>
+        <v>0.07011278195488724</v>
+      </c>
+      <c r="BC16" t="inlineStr"/>
       <c r="BD16" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>-1.370303030303035</v>
-      </c>
+        <v>-2.678181818181816</v>
+      </c>
+      <c r="BE16" t="inlineStr"/>
       <c r="BF16" t="n">
-        <v>-2</v>
+        <v>-0.3369696969696971</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3398,32 +3390,32 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SvbdWyTh</t>
+          <t>foKU4Bi8</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45542.89583333334</v>
+        <v>45549.97916666666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">bazakos f 
+          <t xml:space="preserve">demianchuk s 
   usa </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">soldier field
-  chicago  il </t>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3450,137 +3442,123 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>6LuGZiZI</t>
+          <t>Sd7snoa0</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>nJ01AhXP</t>
+          <t>UFWZoX9L</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>16.5</v>
+        <v>-2.5</v>
       </c>
       <c r="W17" t="n">
-        <v>-16.5</v>
+        <v>-5.75</v>
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0.5</v>
       </c>
       <c r="AB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE17" t="n">
         <v>-2.5</v>
       </c>
-      <c r="AC17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>-6</v>
-      </c>
       <c r="AF17" t="n">
-        <v>4</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>2</v>
-      </c>
+        <v>-1.75</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-7.75</v>
+      </c>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>68.26666666666667</v>
+        <v>67.09166666666667</v>
       </c>
       <c r="AM17" t="n">
-        <v>65.06060606060606</v>
+        <v>66.94444444444444</v>
       </c>
       <c r="AN17" t="n">
-        <v>-1275000</v>
+        <v>-2.015151515151473</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>-0.3111111111111029</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.402525252525251</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>-0.2090909090909179</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>111514.491618539</v>
-      </c>
+        <v>-0.09595959595958448</v>
+      </c>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="n">
-        <v>-154</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.210101010101013</v>
-      </c>
+        <v>-90748.05288913962</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
       <c r="AU17" t="n">
-        <v>-0.009595959595959602</v>
+        <v>0.2036094485224851</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.886491591297087</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>2.387739616250784</v>
-      </c>
+        <v>-496557.5757575757</v>
+      </c>
+      <c r="AW17" t="inlineStr"/>
       <c r="AX17" t="n">
-        <v>-0.9843477579818938</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1000227.272727273</v>
-      </c>
+        <v>-0.7203037831733496</v>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="n">
-        <v>-113</v>
+        <v>-0.2485119518162975</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0.006213450292397615</v>
+        <v>-1.087854884246184</v>
       </c>
       <c r="BB17" t="n">
-        <v>-2.092488354037272</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>-2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BC17" t="inlineStr"/>
       <c r="BD17" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>-1.150505050505043</v>
-      </c>
+        <v>-0.8769696969696987</v>
+      </c>
+      <c r="BE17" t="inlineStr"/>
       <c r="BF17" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3589,32 +3567,32 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hIoLKAg0</t>
+          <t>AHSZqech</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45542.85416666666</v>
+        <v>45549.9375</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">mendoza r 
+          <t xml:space="preserve">szpala l 
   usa </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">lower com field
-  columbus  oh </t>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3641,7 +3619,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>zoZ995af</t>
+          <t>WWvwigh8</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -3650,118 +3628,114 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>-3</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
+        <v>-4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-2</v>
+      </c>
       <c r="Q18" t="n">
-        <v>-2</v>
-      </c>
-      <c r="R18" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>17.75</v>
+        <v>-0.6666666666666661</v>
       </c>
       <c r="W18" t="n">
-        <v>-17.75</v>
+        <v>-5.333333333333334</v>
       </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.5</v>
+        <v>-1</v>
       </c>
       <c r="AB18" t="n">
-        <v>2</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.5</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AD18" t="n">
-        <v>-6.75</v>
+        <v>-10</v>
       </c>
       <c r="AE18" t="n">
-        <v>-5.75</v>
+        <v>10</v>
       </c>
       <c r="AF18" t="n">
-        <v>8.25</v>
+        <v>-2.333333333333334</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>-0.25</v>
-      </c>
+        <v>0.3333333333333339</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-6.000000000000002</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.666666666666668</v>
+      </c>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>67.39204545454545</v>
+        <v>66.94242424242424</v>
       </c>
       <c r="AM18" t="n">
-        <v>68.5060606060606</v>
+        <v>69.57272727272728</v>
       </c>
       <c r="AN18" t="n">
-        <v>50000</v>
-      </c>
-      <c r="AO18" t="inlineStr"/>
+        <v>2.062626262626281</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-4.37398989898989</v>
+      </c>
       <c r="AP18" t="n">
-        <v>-0.4745959595959732</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>2.178571428571473</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>-465626.5609390605</v>
-      </c>
+        <v>-2.143686868686871</v>
+      </c>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="n">
-        <v>63</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>-1.23945165945166</v>
-      </c>
+        <v>-870727.1492094859</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
       <c r="AU18" t="n">
-        <v>-0.1738095238095236</v>
+        <v>-1.321862648221355</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0.7000877638985017</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>-1.31548879509235</v>
-      </c>
+        <v>-943385.1010101009</v>
+      </c>
+      <c r="AW18" t="inlineStr"/>
       <c r="AX18" t="n">
-        <v>-1.537052142231161</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>777626.6233766228</v>
-      </c>
+        <v>-4.085449604743079</v>
+      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="n">
-        <v>63</v>
+        <v>-8.316880764163365</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0.1883312020460359</v>
+        <v>-0.8543437088274004</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.720382005036754</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="n">
-        <v>-1.025721500721506</v>
-      </c>
+      <c r="BD18" t="n">
+        <v>-2.345202020202017</v>
+      </c>
+      <c r="BE18" t="inlineStr"/>
       <c r="BF18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -3770,32 +3744,32 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>KEflYcbt</t>
+          <t>xUcLQXdU</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45542.85416666666</v>
+        <v>45549.89583333334</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ford t 
+          <t xml:space="preserve">touchan r 
   usa </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">gillette stadium
-  foxborough  ma </t>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3822,129 +3796,127 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>rXawJi8t</t>
+          <t>6LuGZiZI</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2PIEeC7j</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>12</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>14</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-1</v>
+      </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>23.5</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>-23.5</v>
+        <v>-2.6</v>
       </c>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>-0.6666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.3333333333333335</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="AB19" t="n">
-        <v>-1.666666666666667</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2</v>
+        <v>0.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>-5.166666666666668</v>
+        <v>-0.4000000000000057</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.5</v>
+        <v>0.4000000000000057</v>
       </c>
       <c r="AF19" t="n">
-        <v>-1.833333333333334</v>
+        <v>-0.3999999999999995</v>
       </c>
       <c r="AG19" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
+        <v>2.6</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>6.8</v>
+      </c>
       <c r="AJ19" t="n">
-        <v>-0.1666666666666666</v>
+        <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.3333333333333333</v>
+        <v>-8</v>
       </c>
       <c r="AL19" t="n">
-        <v>67.3</v>
+        <v>69.05515151515151</v>
       </c>
       <c r="AM19" t="n">
-        <v>68.45757575757575</v>
+        <v>67.98181818181818</v>
       </c>
       <c r="AN19" t="n">
-        <v>5525000</v>
+        <v>2.340909090909037</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>2.933333333333337</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.01084175084176309</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>-1.149932659932603</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>304635.3278630294</v>
-      </c>
+        <v>-1.34999999999998</v>
+      </c>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="n">
-        <v>-62</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0.2468013468013623</v>
-      </c>
+        <v>-210514.4435666462</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
       <c r="AU19" t="n">
-        <v>-0.1271380471380474</v>
+        <v>-2.833708138098871</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.993494448504045</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>3.232414088823951</v>
-      </c>
+        <v>437272.7272727273</v>
+      </c>
+      <c r="AW19" t="inlineStr"/>
       <c r="AX19" t="n">
-        <v>2.02537840498519</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>-221015.1515151516</v>
-      </c>
+        <v>1.908029811848465</v>
+      </c>
+      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="n">
-        <v>-54</v>
+        <v>0.7963888434855306</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.05418868996874115</v>
+        <v>-0.2875149831099577</v>
       </c>
       <c r="BB19" t="n">
-        <v>-1.6858881886088</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2</v>
-      </c>
+        <v>0.01488095238095233</v>
+      </c>
+      <c r="BC19" t="inlineStr"/>
       <c r="BD19" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.404410774410778</v>
-      </c>
+        <v>3.646969696969702</v>
+      </c>
+      <c r="BE19" t="inlineStr"/>
       <c r="BF19" t="n">
-        <v>-1</v>
+        <v>0.09090909090909105</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -3953,32 +3925,32 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>EyfhXHDn</t>
+          <t>EkZQoHSu</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45542.85416666666</v>
+        <v>45549.89583333334</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">touchan r 
+          <t xml:space="preserve">bazakos f 
   usa </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  harrison  nj </t>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4005,137 +3977,1545 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>rJ9D8rzj</t>
+          <t>86yPt28f</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>txm4BKVR</t>
+          <t>GzULyFoh</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
-      </c>
-      <c r="R20" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3</v>
+      </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.166666666666667</v>
+        <v>0.1499999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3333333333333357</v>
+        <v>-0.9000000000000004</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3333333333333357</v>
+        <v>0.75</v>
       </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.333333333333333</v>
+        <v>-0.95</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.3333333333333339</v>
+        <v>5.5</v>
       </c>
       <c r="AE20" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-0.5499999999999998</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="n">
+        <v>70.36363636363636</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>68.65555555555557</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.904848484848515</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>2.192222222222227</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>-0.4252525252525174</v>
+      </c>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="n">
+        <v>-310265.843401649</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="n">
+        <v>-1.174855067259159</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>297681.8181818179</v>
+      </c>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="n">
+        <v>-1.032890624105463</v>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="n">
+        <v>-0.8295231849707392</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>-1.58129393340397</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="n">
+        <v>2.240404040404044</v>
+      </c>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="n">
+        <v>0.1939393939393941</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>htYUpyrn</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45549.89583333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">demianchuk s 
+  usa </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>167</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-3.15</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.2999999999999998</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-6.299999999999997</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>6.299999999999997</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-0.1999999999999993</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="n">
+        <v>69.08787878787878</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>68.87777777777778</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.525757575757609</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>2.12060606060605</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0.8466666666666782</v>
+      </c>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="n">
+        <v>-195579.6031131751</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="n">
+        <v>-0.2022921888053588</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>902503.0303030305</v>
+      </c>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="n">
+        <v>-1.565357941422185</v>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="n">
+        <v>-1.443798528183201</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>3.916638102609454</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="n">
+        <v>0.1966666666666654</v>
+      </c>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="n">
+        <v>0.184848484848485</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>vquIRDsO</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>167</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>WSL0wFD4</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.05000000000000004</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.700000000000003</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>-1.700000000000003</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.8499999999999996</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>-6.85</v>
+      </c>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="n">
+        <v>67.01767676767676</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>67.35737373737375</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>-1.554814814814819</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>2.364814814814821</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.508148148148138</v>
+      </c>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="n">
+        <v>1917351.596435675</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="n">
+        <v>0.4499066293183915</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>387759.2592592593</v>
+      </c>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="n">
+        <v>0.2993450520304748</v>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="n">
+        <v>1.093517841919365</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>-0.2440540467394499</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0.290573282453078</v>
+      </c>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="n">
+        <v>-0.2818518518518474</v>
+      </c>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="n">
+        <v>-0.03222222222222215</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>lfn5UFc5</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>167</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.1499999999999999</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.05000000000000004</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>6.449999999999999</v>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-0.9500000000000002</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-0.6499999999999999</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.8500000000000001</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.299999999999997</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>-1.299999999999997</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>-0.4000000000000004</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="n">
+        <v>67.49974747474747</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>68.02449494949495</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.5554208754208787</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>-0.2715151515151746</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.7661616161616109</v>
+      </c>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="n">
+        <v>26174.26489573205</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="n">
+        <v>-3.58657845777411</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>-592015.8249158254</v>
+      </c>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="n">
+        <v>-0.1584091331373934</v>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="n">
+        <v>-3.205977144835849</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.115181195615975</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="n">
+        <v>-1.270370370370372</v>
+      </c>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>dKkDSgSH</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chase stadium
+  fort lauderdale  fl </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>167</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>7</v>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="n">
+        <v>68.63181818181818</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>65.94015151515151</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0.2445454545454879</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>-0.09363636363636374</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>2.631363636363631</v>
+      </c>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="n">
+        <v>1040922.98085901</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="n">
+        <v>4.867264239028941</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1406750</v>
+      </c>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="n">
+        <v>-1.708169934640523</v>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="n">
+        <v>2.927307422969193</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0.2470016339869403</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>-0.04896708683473383</v>
+      </c>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="n">
+        <v>-1.727727272727265</v>
+      </c>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="n">
+        <v>0.3509090909090908</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ITj9TZCB</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>167</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>-5</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1</v>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>-8.75</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>66.08484848484849</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>68.65000000000001</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0.7399494949495136</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1.270050505050492</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>-3.080454545454543</v>
+      </c>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="n">
+        <v>-416514.7446937306</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="n">
+        <v>-2.190421358655101</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>-223880.0505050507</v>
+      </c>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="n">
+        <v>0.5529953448684068</v>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="n">
+        <v>-1.061906278619908</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>2.819360716854504</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>-0.07766161616161593</v>
+      </c>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="n">
+        <v>4.355353535353537</v>
+      </c>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="n">
+        <v>0.07818181818181857</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>jDDw3kMK</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo field
+  toronto  on </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>167</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.4166666666666665</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="n">
+        <v>68.03181818181818</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>67.75227272727273</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>-0.4238383838383868</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0.1957575757575825</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0.7428282828282704</v>
+      </c>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="n">
+        <v>614032.9976786494</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="n">
+        <v>0.7144386410690657</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>447804.0404040399</v>
+      </c>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="n">
+        <v>-4.073922140661274</v>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="n">
+        <v>-2.722940742832044</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.914720653742364</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0.003824424367902424</v>
+      </c>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="n">
+        <v>-0.5391919191919214</v>
+      </c>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="n">
+        <v>0.05494949494949486</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>8lOY3V6E</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">da silva a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>167</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
         <v>3</v>
       </c>
-      <c r="AF20" t="n">
-        <v>-1.666666666666666</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>-5.333333333333333</v>
-      </c>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="n">
-        <v>-0.1666666666666667</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>-0.1666666666666667</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>67.63636363636364</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>69.05</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>-2975000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>4.666753246753245</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>-0.492207792207779</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>173528.0265056582</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>-146</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>-0.3070129870129961</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>-0.05194805194805197</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>-2.853811282157967</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>-1.016499227317311</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>3.160885638008054</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>838090.9090909089</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>-149</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>-0.08446115288220568</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.819385172417213</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>4.666666666666657</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>-7.666666666666668</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>-5.233506493506493</v>
-      </c>
-      <c r="BF20" t="n">
+      <c r="P27" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V27" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W27" t="n">
+        <v>6</v>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>67.58636363636364</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>67.06363636363636</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>-1.050707070707119</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>-2.032929292929296</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>-0.3165656565656718</v>
+      </c>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="n">
+        <v>-377497.4234441016</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="n">
+        <v>1.340272341514094</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>-744575.7575757576</v>
+      </c>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="n">
+        <v>-1.756971174157201</v>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="n">
+        <v>0.5812171529731103</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>-4.627701854613264</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0.08704146730462514</v>
+      </c>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="n">
+        <v>-2.583838383838383</v>
+      </c>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="n">
+        <v>0.07454545454545469</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>A3m1Vera</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>167</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>63fk89be</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC28" t="n">
         <v>-2</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="AD28" t="n">
+        <v>-11.75</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="n">
+        <v>67.93712121212121</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>69.53484848484848</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>-3.510909090909081</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>-0.7909090909090821</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>-0.2363636363636346</v>
+      </c>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="n">
+        <v>882534.2381689518</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="n">
+        <v>4.817441029043195</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>-1592172.727272727</v>
+      </c>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="n">
+        <v>-1.166643078283936</v>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="n">
+        <v>2.574118384195785</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>-3.867387586613575</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="n">
+        <v>0.178181818181816</v>
+      </c>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="n">
+        <v>-0.0363636363636366</v>
+      </c>
+      <c r="BG28" t="n">
         <v>0</v>
       </c>
     </row>
